--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486794_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486794_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8193</v>
+        <v>4.9433</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1708</v>
+        <v>4.5805</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6484</v>
+        <v>0.3627</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3216</v>
+        <v>1.2482</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1106</v>
+        <v>0.0411</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.789</v>
+        <v>1.2071</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9232</v>
+        <v>1.4153</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0768</v>
+        <v>0.1109</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.1536</v>
+        <v>1.3044</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3985</v>
+        <v>-0.1671</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0338</v>
+        <v>-0.0698</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6354</v>
+        <v>-0.0973</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1035</v>
+        <v>-0.6758</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2477</v>
+        <v>0.096</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8558</v>
+        <v>-0.7718</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6565</v>
+        <v>2.8262</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.0692</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6565</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8484</v>
+        <v>4.4055</v>
       </c>
       <c r="E3" t="n">
-        <v>3.436</v>
+        <v>1.1295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4124</v>
+        <v>3.276</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2482</v>
+        <v>1.3216</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0411</v>
+        <v>2.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2071</v>
+        <v>-0.789</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4153</v>
+        <v>0.9232</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1109</v>
+        <v>1.0768</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3044</v>
+        <v>-0.1536</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1671</v>
+        <v>0.3985</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0698</v>
+        <v>1.0338</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0973</v>
+        <v>-0.6354</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7707</v>
+        <v>0.6897</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0486</v>
+        <v>0.2064</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7221</v>
+        <v>0.4833</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8262</v>
+        <v>0.6565</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0692</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.243</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1722</v>
+        <v>3.4205</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7884</v>
+        <v>2.1608</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3838</v>
+        <v>1.2597</v>
       </c>
       <c r="G4" t="n">
         <v>1.827</v>
@@ -766,13 +766,13 @@
         <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6621</v>
+        <v>0.9104</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0548</v>
+        <v>0.4272</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6073</v>
+        <v>0.4831</v>
       </c>
       <c r="V4" t="n">
         <v>1.8415</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9062</v>
+        <v>0.931</v>
       </c>
       <c r="E5" t="n">
         <v>0.5725</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3337</v>
+        <v>0.3585</v>
       </c>
       <c r="G5" t="n">
         <v>0.8895999999999999</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3696</v>
+        <v>-0.3448</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.139</v>
+        <v>-0.2037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0611</v>
+        <v>-0.0285</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2</v>
+        <v>-0.1752</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4987</v>
@@ -922,13 +922,13 @@
         <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3751</v>
+        <v>0.3104</v>
       </c>
       <c r="T6" t="n">
-        <v>0.358</v>
+        <v>0.2685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.017</v>
+        <v>0.0419</v>
       </c>
       <c r="V6" t="n">
         <v>0.3709</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.803</v>
+        <v>-0.7533</v>
       </c>
       <c r="E7" t="n">
         <v>-1.2496</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4466</v>
+        <v>0.4963</v>
       </c>
       <c r="G7" t="n">
         <v>0.3224</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.353</v>
+        <v>-0.3034</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0332</v>
+        <v>0.0829</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.299</v>
+        <v>-0.9403</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6289</v>
+        <v>0.7392</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9278</v>
+        <v>-1.6795</v>
       </c>
       <c r="G8" t="n">
         <v>0.1496</v>
@@ -1078,13 +1078,13 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9932</v>
+        <v>-0.6345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0555</v>
+        <v>0.0548</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9376</v>
+        <v>-0.6893</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9256</v>
+        <v>-1.5931</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8342</v>
+        <v>-1.6756</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0914</v>
+        <v>0.0825</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1863</v>
@@ -1156,13 +1156,13 @@
         <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9323</v>
+        <v>-0.5999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4966</v>
+        <v>-0.338</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4357</v>
+        <v>-0.2619</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3583</v>
+        <v>-1.9183</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.256</v>
+        <v>-1.8906</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1022</v>
+        <v>-0.0277</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8935999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2759</v>
+        <v>0.0895</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3282</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1348</v>
+        <v>-3.2992</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0625</v>
+        <v>-2.2065</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0724</v>
+        <v>-1.0927</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1663</v>
+        <v>-1.4551</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3932</v>
+        <v>-1.3172</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7732</v>
+        <v>-0.1379</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9723</v>
+        <v>-1.3169</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.634</v>
+        <v>-0.6274</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3383</v>
+        <v>-0.6895</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.194</v>
+        <v>-0.1382</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7591</v>
+        <v>-0.6898</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5651</v>
+        <v>0.5516</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.127</v>
+        <v>-0.1724</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9099</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0368</v>
+        <v>-0.2481</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-0.8995</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1914</v>
+        <v>-3.7043</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3846</v>
+        <v>-1.7312</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8068</v>
+        <v>-1.973</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1787</v>
+        <v>-2.1663</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7997</v>
+        <v>-1.3932</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.379</v>
+        <v>-0.7732</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5083</v>
+        <v>-1.9723</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3162</v>
+        <v>-0.634</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.192</v>
+        <v>-1.3383</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6704</v>
+        <v>-0.194</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4835</v>
+        <v>-0.7591</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1869</v>
+        <v>0.5651</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S12" t="n">
-        <v>0.717</v>
+        <v>-0.6964</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0199</v>
+        <v>0.2411</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3028</v>
+        <v>-0.9375</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5572</v>
+        <v>-3.8464</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3651</v>
+        <v>-2.7913</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1921</v>
+        <v>-1.0551</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4551</v>
+        <v>-2.1787</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3172</v>
+        <v>-0.7997</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1379</v>
+        <v>-1.379</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3169</v>
+        <v>-0.5083</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6274</v>
+        <v>-0.3162</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6895</v>
+        <v>-0.192</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1382</v>
+        <v>-1.6704</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6898</v>
+        <v>-0.4835</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5516</v>
+        <v>-1.1869</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4303</v>
+        <v>0.0619</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0828</v>
+        <v>0.6131</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3475</v>
+        <v>-0.5512</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8995</v>
+        <v>-0.5712</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8995</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.6622</v>
+        <v>-2.558299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4943</v>
+        <v>-2.3908</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1678000000000006</v>
+        <v>-0.1675000000000002</v>
       </c>
       <c r="G14" t="n">
         <v>-2.620300000000001</v>
@@ -1546,13 +1546,13 @@
         <v>9.654</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.482499999999999</v>
+        <v>-1.379</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1342</v>
+        <v>1.2377</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6166</v>
+        <v>-2.6167</v>
       </c>
       <c r="V14" t="n">
         <v>1.4408</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5379</v>
+        <v>8.0938</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9192</v>
+        <v>7.2987</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6187</v>
+        <v>0.7951</v>
       </c>
       <c r="G15" t="n">
         <v>3.4805</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8992</v>
+        <v>0.4551</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1578</v>
+        <v>0.5372</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2586</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.8066</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1473</v>
+        <v>3.2794</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3728</v>
+        <v>2.3036</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7746</v>
+        <v>0.9759</v>
       </c>
       <c r="G16" t="n">
         <v>3.2672</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.27</v>
+        <v>0.8621</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4417</v>
+        <v>0.4891</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1717</v>
+        <v>0.373</v>
       </c>
       <c r="V16" t="n">
         <v>0.3086</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9412</v>
+        <v>3.2086</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5927</v>
+        <v>1.5235</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3486</v>
+        <v>1.6851</v>
       </c>
       <c r="G17" t="n">
         <v>2.1165</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1364</v>
+        <v>0.131</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6624</v>
+        <v>0.2684</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.474</v>
+        <v>-0.1374</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3905</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2141</v>
+        <v>-0.3197</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4297</v>
+        <v>-0.74</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6438</v>
+        <v>0.4203</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0437</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6785</v>
+        <v>0.1447</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1377</v>
+        <v>-0.1726</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.3174</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1619</v>
+        <v>-1.3809</v>
       </c>
       <c r="E19" t="n">
-        <v>0.732</v>
+        <v>-3.0678</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5701000000000001</v>
+        <v>1.6869</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8182</v>
+        <v>-0.9376</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6419</v>
+        <v>-3.6414</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1763</v>
+        <v>2.7038</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7114</v>
+        <v>-0.7987</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1943</v>
+        <v>-1.9857</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9057</v>
+        <v>1.1869</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5296</v>
+        <v>-0.1388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5524</v>
+        <v>-1.6557</v>
       </c>
       <c r="O19" t="n">
-        <v>2.082</v>
+        <v>1.5169</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>-2.1239</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>2.6754</v>
+        <v>-0.007</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3162</v>
+        <v>-0.1452</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3592</v>
+        <v>0.1382</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.3318</v>
+        <v>0.7221</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6174</v>
+        <v>0.7221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6919</v>
+        <v>-1.3965</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3143</v>
+        <v>-0.7159</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3776</v>
+        <v>-0.6805</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6213</v>
+        <v>0.8182</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4758</v>
+        <v>0.6419</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8545</v>
+        <v>0.1763</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7098</v>
+        <v>-0.7114</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7167</v>
+        <v>1.1943</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0069</v>
+        <v>-1.9057</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0885</v>
+        <v>1.5296</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7591</v>
+        <v>-0.5524</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8477</v>
+        <v>2.082</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.5792</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4853</v>
+        <v>1.1171</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6891</v>
+        <v>0.8683</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2038</v>
+        <v>0.2488</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9421</v>
+        <v>-3.3318</v>
       </c>
       <c r="W20" t="n">
         <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>-3.6174</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8211</v>
+        <v>-1.515</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.073</v>
+        <v>-0.8662</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7481</v>
+        <v>-0.6488</v>
       </c>
       <c r="G21" t="n">
         <v>-0.922</v>
@@ -2092,13 +2092,13 @@
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1269</v>
+        <v>0.1793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3311</v>
+        <v>-0.1242</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2042</v>
+        <v>0.3036</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0856</v>
+        <v>-1.5911</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5849</v>
+        <v>-1.6246</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4993</v>
+        <v>0.0335</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9376</v>
+        <v>-1.6213</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.6414</v>
+        <v>-2.4758</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7038</v>
+        <v>0.8545</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7987</v>
+        <v>-1.7098</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9857</v>
+        <v>-1.7167</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1869</v>
+        <v>0.0069</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1388</v>
+        <v>0.0885</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6557</v>
+        <v>-0.7591</v>
       </c>
       <c r="O22" t="n">
-        <v>1.5169</v>
+        <v>0.8477</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1239</v>
+        <v>-0.5792</v>
       </c>
       <c r="R22" t="n">
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7117</v>
+        <v>0.5861</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6623</v>
+        <v>0.3789</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0494</v>
+        <v>0.2072</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7221</v>
+        <v>-0.9421</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7221</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7417</v>
+        <v>-3.3377</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.047</v>
+        <v>-3.9436</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3053</v>
+        <v>0.6059</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5378</v>
@@ -2248,13 +2248,13 @@
         <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0109</v>
+        <v>0.3932</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4135</v>
+        <v>0.5169</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4243</v>
+        <v>-0.1237</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.662100000000001</v>
+        <v>5.040900000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1678000000000006</v>
+        <v>0.1677</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4945</v>
+        <v>4.8734</v>
       </c>
       <c r="G24" t="n">
         <v>2.62</v>
@@ -2326,13 +2326,13 @@
         <v>9.653900000000002</v>
       </c>
       <c r="S24" t="n">
-        <v>2.4825</v>
+        <v>3.8616</v>
       </c>
       <c r="T24" t="n">
         <v>2.6168</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1342</v>
+        <v>1.245</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4409</v>
